--- a/Target Folder/QA-Files/zh-CN/MarsQA-202502101821-1617.xlsx
+++ b/Target Folder/QA-Files/zh-CN/MarsQA-202502101821-1617.xlsx
@@ -46,13 +46,13 @@
   <si>
     <r>
       <rPr/>
-      <t>原文</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>译文</t>
+      <t>来源</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>目标</t>
     </r>
   </si>
   <si>
@@ -82,19 +82,19 @@
   <si>
     <r>
       <rPr/>
-      <t>译文不一致</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号36)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>实施过程可能还包括与家长/监护人以及 IEP 团队的其他成员协商并建立教学策略模型</t>
+      <t>目标不一致</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号36)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>实施可能还包括与家长/监护人以及 IEP 团队的其他成员进行教学策略咨询和建模</t>
     </r>
   </si>
   <si>
@@ -106,13 +106,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号97)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>实施过程可能还包括与家长/监护人以及 IEP 团队的其他成员协商并建立教学策略模型。</t>
+      <t>任务 1055 [英(美)译葡].docx(编号97)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>实施可能还包括与家长/监护人以及 IEP 团队的其他成员进行教学策略咨询和建模。</t>
     </r>
   </si>
   <si>
@@ -195,37 +195,37 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号159)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号215)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号275)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号328)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>译文与原文相同</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号376)</t>
+      <t>任务 1055 [英(美)译葡].docx(编号159)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号215)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号275)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号328)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>目标与来源相同</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号376)</t>
     </r>
   </si>
   <si>
@@ -250,13 +250,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号8)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>在 3 个连续的数据收集点中，Jorge 将在 5 次试验中的 4 次，在课堂环境中，使用 10 个不同的四词话语来表达他的愿望和需求</t>
+      <t>任务 1055 [英(美)译葡].docx(编号8)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>Jorge 将使用 10 种不同的四词短语，在连续 3 个数据收集点中，在 5 次尝试中的 4 次，表达他在课堂环境中的需求</t>
     </r>
   </si>
   <si>
@@ -275,13 +275,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号37)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>在学校上课期间，与 Jorge 合作的言语治疗师将模拟以下策略，以促进课外技能的推广</t>
+      <t>任务 1055 [英(美)译葡].docx(编号37)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>在学校的课程中，与 Jorge 合作的言语治疗师将模拟以下策略，以促进技能在课程外的延续</t>
     </r>
     <r>
       <rPr>
@@ -307,13 +307,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号42)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>将所需的物品（例如，电视遥控器）放入带盖的透明塑料箱中，这样 Jorge 就可以看到物品，但需要“帮助”才能“打开”箱子并取出所需的物品</t>
+      <t>任务 1055 [英(美)译葡].docx(编号42)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>将所需的物品（例如电视遥控器）放入带盖的透明塑料容器中，这样 Jorge 就可以看到物品，但需要“帮助”才能“打开”容器并取出所需的物品</t>
     </r>
   </si>
   <si>
@@ -332,13 +332,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号51)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>提供选择，例如“我们需要书写。</t>
+      <t>任务 1055 [英(美)译葡].docx(编号51)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>提供选择，例如“我们需要写字。”</t>
     </r>
   </si>
   <si>
@@ -357,13 +357,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号52)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>你需要什么，铅笔还是蜡笔？”。</t>
+      <t>任务 1055 [英(美)译葡].docx(编号52)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>你需要什么，铅笔还是蜡笔？”</t>
     </r>
   </si>
   <si>
@@ -386,13 +386,26 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号62)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>对以下任务的每次观察使用“是/否”记录，并记录引发响应所需的提示的数量和类型</t>
+      <t>任务 1055 [英(美)译葡].docx(编号62)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>Use "yes/no" record for each observation of the following tasks, with record of the number and type of prompts required to elicit the response</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <color indexed="10"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>以下任务的每次观察均使用“是/否”记录，并记录引出响应所需的提示数量和类型</t>
     </r>
     <r>
       <rPr>
@@ -405,7 +418,26 @@
   <si>
     <r>
       <rPr/>
-      <t>以下のタスクの観察ごとに「はい/いいえ」の記録を使用し、回答を引き出すために必要なプロンプトの数と種類を記録します</t>
+      <t>任务 1055 [英(美)译葡].docx(编号63)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>This goal will be considered achieved when Jorge can</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <color indexed="10"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>当豪尔赫能够做到以下几点时，该目标将被视为已实现</t>
     </r>
     <r>
       <rPr>
@@ -418,30 +450,63 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号63)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>当豪尔赫能够</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t>时，此目标将被视为已实现</t>
-    </r>
-    <r>
-      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号74)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号75)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>After reviewing the outcome/goal and progress monitoring data, we, the team, have decided</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <color indexed="10"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>在审查了结果/目标和进度监测数据后，我们团队决定</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <color indexed="10"/>
+      </rPr>
       <t>：</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>この目標は、ホルヘが次のことができる場合に達成されたと見なされます</t>
+      <t>任务 1055 [英(美)译葡].docx(编号133)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号178)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>This goal will be monitored and data collected by family and behavior support specialist weekly</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>此目标将由家庭和行为支持专家每周监测并收集数据</t>
     </r>
     <r>
       <rPr>
@@ -454,19 +519,32 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号74)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号75)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>在审查了结果/目标和进度监测数据后，我们团队决定</t>
+      <t>任务 1055 [英(美)译葡].docx(编号189)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号216)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>Teaching strategies recommended are</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <color indexed="10"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>推荐的教学策略有</t>
     </r>
     <r>
       <rPr>
@@ -479,289 +557,152 @@
   <si>
     <r>
       <rPr/>
-      <t>結果/目標および進捗監視データを確認した後、私たちチームは次のことを決定しました</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
+      <t>任务 1055 [英(美)译葡].docx(编号237)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号248)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号292)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号303)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号364)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>标点符号前间距不正确</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号48)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>For example, begin with "What is this?" and then move on to "What color is this?" or "What can you do with this?"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>例如</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <color indexed="10"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr/>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <color indexed="10"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr/>
+      <t>以“这是什么？”开头，然后转到“这是什么颜色？”或“你能用它做什么？”“这是什么颜色？”或“你能用它做什么？”」</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>鉛筆やクレヨンは何が必要ですか</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <color indexed="10"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr/>
+      <t>?</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <color indexed="10"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr/>
+      <t>」</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <color indexed="10"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr/>
       <t>。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号133)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号178)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>此目标将由家庭和行为支持专家每周监测并收集数据</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>この目標は、家族や行動サポートスペシャリストによって毎週監視され、データが収集されます</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号189)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号216)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>推荐的教学策略是</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t>：</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>推奨される教育戦略は次のとおりです</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号237)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号248)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号292)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号303)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号364)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>标点符号前间距不正确</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号48)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>例如，以“这是什么？”开头，然后转到“这是什么颜色？”或“你能用它做什么？”</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>たとえば</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>「 これは何ですか</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>?</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>」 で始まります。「これは何色？」に移ります「これで何ができる？」</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>铅笔还是蜡笔，你需要什么</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>?</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>」</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号269)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>豪尔赫有时会拒绝完成某些活动，会说“不”或“因为我不想”。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>ホルヘは時々特定の活動を完了することを拒否し</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>「 いいえ」または「したくないので」と言います。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号370)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>PCA 正在帮助豪尔赫使用计时器、视觉时间表从活动中过渡，并在过渡前提供短暂的运动休息，我们将继续努力提高他的依从性。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>PCAは、ホルヘがタイマー</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>、 ビジュアルスケジュールを使用して活動から移行するのを支援し、移行前に短い移動休憩を提供しており、引き続き彼のコンプライアンスを高めていきます。</t>
+      <t>任务 1055 [英(美)译葡].docx(编号269)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>Jorge will sometimes refuse to complete certain activities and will say "No" or "because I don't want to."</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>豪尔赫有时会拒绝完成某些活动，并会说“不”或“因为我不想”。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号370)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>The PCA is helping Jorge transition from activities using timer ,visual schedule, and providing short movement breaks before transition, we will continue working to increase his compliance.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>PCA 正在帮助豪尔赫使用计时器、视觉时间表从活动中过渡，并在过渡前提供短暂的活动休息，我们将继续努力提高他的依从性。</t>
     </r>
   </si>
   <si>
@@ -773,7 +714,7 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号380)</t>
+      <t>任务 1055 [英(美)译葡].docx(编号380)</t>
     </r>
   </si>
   <si>
@@ -806,13 +747,13 @@
     </r>
     <r>
       <rPr/>
-      <t>株式会社エルウィン</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>Numeric Mismatch</t>
+      <t>ELWYN 公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>数字不匹配</t>
     </r>
   </si>
   <si>
@@ -835,13 +776,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号60)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>-Re-evaluation will occur every two years.</t>
+      <t>任务 1055 [英(美)译葡].docx(编号60)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>-每两年进行一次重新评估。</t>
     </r>
   </si>
   <si>
@@ -864,13 +805,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号64)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>use 10 different three word utterances to express his wants and needs in his classroom setting in 4 out of 5 trials</t>
+      <t>任务 1055 [英(美)译葡].docx(编号64)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>在5次尝试中，有4次在课堂上使用10种不同的三个词语来表达他的愿望和需求</t>
     </r>
   </si>
   <si>
@@ -893,13 +834,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号65)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>-use 5 different four word utterances to express his wants and needs in his classroom setting in 4 out of 5 trials</t>
+      <t>任务 1055 [英(美)译葡].docx(编号65)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>-在5次尝试中，有4次在课堂上使用5种不同的四个词语来表达他的愿望和需求</t>
     </r>
   </si>
   <si>
@@ -922,13 +863,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号66)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>-use 10 different four word utterances to express his wants and needs in his classroom setting in 4 out of 5 trials</t>
+      <t>任务 1055 [英(美)译葡].docx(编号66)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>-在5次尝试中，有4次在课堂上使用10种不同的四个词语来表达他的愿望和需求</t>
     </r>
   </si>
   <si>
@@ -951,13 +892,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号123)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>Progress monitoring reports will be shared with the family twice annually.</t>
+      <t>任务 1055 [英(美)译葡].docx(编号123)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>进度监测报告将每年两次与家人分享。</t>
     </r>
   </si>
   <si>
@@ -980,19 +921,19 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号179)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号203)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>Given verbal and visual prompts and models faded to elimination, Jorge will sustain social interaction during reciprocal play activities, with adults and peers in four out of five consecutive trials.</t>
+      <t>任务 1055 [英(美)译葡].docx(编号179)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号203)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>在口头和视觉提示以及逐渐消失的模型下，豪尔赫将在连续五次尝试中的四次中，在与成人和同伴的互动游戏活动中保持社交互动。</t>
     </r>
   </si>
   <si>
@@ -1026,13 +967,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号228)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>-Engages in two play exchanges with an adult or child during self-selected play</t>
+      <t>任务 1055 [英(美)译葡].docx(编号228)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>-在自主选择的游戏中与成人或儿童进行两次游戏互动</t>
     </r>
   </si>
   <si>
@@ -1055,13 +996,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号229)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>-Participates in a reciprocal play activity with a peer for at least three minutes</t>
+      <t>任务 1055 [英(美)译葡].docx(编号229)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>-与同伴进行至少三分钟的互动游戏活动</t>
     </r>
   </si>
   <si>
@@ -1084,37 +1025,37 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号238)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号247)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号293)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号354)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>Extra Space</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>たとえば</t>
+      <t>任务 1055 [英(美)译葡].docx(编号238)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号247)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号293)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号354)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>多余的空格</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>例如</t>
     </r>
     <r>
       <rPr>
@@ -1125,7 +1066,7 @@
     </r>
     <r>
       <rPr/>
-      <t>、</t>
+      <t>，</t>
     </r>
     <r>
       <rPr>
@@ -1136,41 +1077,19 @@
     </r>
     <r>
       <rPr/>
-      <t>「</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>これは何ですか ? 」</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>で始まります。「これは何色？」に移ります「これで何ができる？」</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号91)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>He can imitate the play actions of adults and children; however, Jorge does not engage in reciprocal play with exchanges.</t>
+      <t>以“这是什么？”开头，然后转到“这是什么颜色？”或“你能用它做什么？”“这是什么颜色？”或“你能用它做什么？”」</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号91)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>他可以模仿成人和儿童的游戏动作；然而，豪尔赫不参与互动游戏。</t>
     </r>
   </si>
   <si>
@@ -1193,86 +1112,31 @@
   <si>
     <r>
       <rPr/>
-      <t>ホルヘは時々特定の活動を完了することを拒否し</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>「</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>いいえ」または「したくないので」と言います。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>PCAは、ホルヘがタイマー</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>ビジュアルスケジュールを使用して活動から移行するのを支援し、移行前に短い移動休憩を提供しており、引き続き彼のコンプライアンスを高めていきます。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>Repeated Words</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号32)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>What teaching strategies are needed to reach the outcome/goal?</t>
+      <t>豪尔赫有时会拒绝完成某些活动，并会说“不”或“因为我不想”。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>PCA 正在帮助豪尔赫使用计时器、视觉时间表从活动中过渡，并在过渡前提供短暂的活动休息，我们将继续努力提高他的依从性。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>重复的词语</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号32)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>需要哪些教学策略来实现结果/目标？</t>
     </r>
     <r>
       <rPr>
@@ -1283,7 +1147,7 @@
     </r>
     <r>
       <rPr/>
-      <t>Include specially designed instruction, supplementary aids and program personnel supports, home or program modifications and training and materials needed by the family or team.</t>
+      <t>包括专门设计的指导、辅助工具和项目人员支持、家庭或项目修改以及家庭或团队所需的培训和材料。</t>
     </r>
   </si>
   <si>
@@ -1324,31 +1188,31 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号93)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号155)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号210)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号270)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号324)</t>
+      <t>任务 1055 [英(美)译葡].docx(编号93)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号155)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号210)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号270)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号324)</t>
     </r>
   </si>
   <si>
@@ -1366,13 +1230,13 @@
   <si>
     <r>
       <rPr/>
-      <t>原文</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>译文</t>
+      <t>来源</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>目标</t>
     </r>
   </si>
   <si>
@@ -1396,19 +1260,19 @@
   <si>
     <r>
       <rPr/>
-      <t>译文不一致</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号36)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>实施过程可能还包括与家长/监护人以及 IEP 团队的其他成员协商并建立教学策略模型</t>
+      <t>目标不一致</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号36)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>实施可能还包括与家长/监护人以及 IEP 团队的其他成员进行教学策略咨询和建模</t>
     </r>
   </si>
   <si>
@@ -1420,13 +1284,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号97)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>实施过程可能还包括与家长/监护人以及 IEP 团队的其他成员协商并建立教学策略模型。</t>
+      <t>任务 1055 [英(美)译葡].docx(编号97)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>实施可能还包括与家长/监护人以及 IEP 团队的其他成员进行教学策略咨询和建模。</t>
     </r>
   </si>
   <si>
@@ -1509,37 +1373,37 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号159)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号215)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号275)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号328)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>译文与原文相同</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号376)</t>
+      <t>任务 1055 [英(美)译葡].docx(编号159)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号215)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号275)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号328)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>目标与来源相同</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号376)</t>
     </r>
   </si>
   <si>
@@ -1564,13 +1428,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号8)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>在 3 个连续的数据收集点中，Jorge 将在 5 次试验中的 4 次，在课堂环境中，使用 10 个不同的四词话语来表达他的愿望和需求</t>
+      <t>任务 1055 [英(美)译葡].docx(编号8)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>Jorge 将使用 10 种不同的四词短语，在连续 3 个数据收集点中，在 5 次尝试中的 4 次，表达他在课堂环境中的需求</t>
     </r>
   </si>
   <si>
@@ -1589,13 +1453,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号37)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>在学校上课期间，与 Jorge 合作的言语治疗师将模拟以下策略，以促进课外技能的推广</t>
+      <t>任务 1055 [英(美)译葡].docx(编号37)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>在学校的课程中，与 Jorge 合作的言语治疗师将模拟以下策略，以促进技能在课程外的延续</t>
     </r>
     <r>
       <rPr>
@@ -1621,13 +1485,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号42)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>将所需的物品（例如，电视遥控器）放入带盖的透明塑料箱中，这样 Jorge 就可以看到物品，但需要“帮助”才能“打开”箱子并取出所需的物品</t>
+      <t>任务 1055 [英(美)译葡].docx(编号42)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>将所需的物品（例如电视遥控器）放入带盖的透明塑料容器中，这样 Jorge 就可以看到物品，但需要“帮助”才能“打开”容器并取出所需的物品</t>
     </r>
   </si>
   <si>
@@ -1646,13 +1510,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号51)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>提供选择，例如“我们需要书写。</t>
+      <t>任务 1055 [英(美)译葡].docx(编号51)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>提供选择，例如“我们需要写字。”</t>
     </r>
   </si>
   <si>
@@ -1671,13 +1535,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号52)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>你需要什么，铅笔还是蜡笔？”。</t>
+      <t>任务 1055 [英(美)译葡].docx(编号52)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>你需要什么，铅笔还是蜡笔？”</t>
     </r>
   </si>
   <si>
@@ -1700,13 +1564,26 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号62)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>对以下任务的每次观察使用“是/否”记录，并记录引发响应所需的提示的数量和类型</t>
+      <t>任务 1055 [英(美)译葡].docx(编号62)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>Use "yes/no" record for each observation of the following tasks, with record of the number and type of prompts required to elicit the response</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <color indexed="10"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>以下任务的每次观察均使用“是/否”记录，并记录引出响应所需的提示数量和类型</t>
     </r>
     <r>
       <rPr>
@@ -1719,7 +1596,26 @@
   <si>
     <r>
       <rPr/>
-      <t>以下のタスクの観察ごとに「はい/いいえ」の記録を使用し、回答を引き出すために必要なプロンプトの数と種類を記録します</t>
+      <t>任务 1055 [英(美)译葡].docx(编号63)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>This goal will be considered achieved when Jorge can</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <color indexed="10"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>当豪尔赫能够做到以下几点时，该目标将被视为已实现</t>
     </r>
     <r>
       <rPr>
@@ -1732,30 +1628,63 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号63)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>当豪尔赫能够</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t>时，此目标将被视为已实现</t>
-    </r>
-    <r>
-      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号74)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号75)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>After reviewing the outcome/goal and progress monitoring data, we, the team, have decided</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <color indexed="10"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>在审查了结果/目标和进度监测数据后，我们团队决定</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <color indexed="10"/>
+      </rPr>
       <t>：</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>この目標は、ホルヘが次のことができる場合に達成されたと見なされます</t>
+      <t>任务 1055 [英(美)译葡].docx(编号133)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号178)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>This goal will be monitored and data collected by family and behavior support specialist weekly</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>此目标将由家庭和行为支持专家每周监测并收集数据</t>
     </r>
     <r>
       <rPr>
@@ -1768,19 +1697,32 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号74)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号75)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>在审查了结果/目标和进度监测数据后，我们团队决定</t>
+      <t>任务 1055 [英(美)译葡].docx(编号189)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号216)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>Teaching strategies recommended are</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <color indexed="10"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>推荐的教学策略有</t>
     </r>
     <r>
       <rPr>
@@ -1793,289 +1735,152 @@
   <si>
     <r>
       <rPr/>
-      <t>結果/目標および進捗監視データを確認した後、私たちチームは次のことを決定しました</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
+      <t>任务 1055 [英(美)译葡].docx(编号237)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号248)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号292)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号303)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号364)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>标点符号前间距不正确</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号48)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>For example, begin with "What is this?" and then move on to "What color is this?" or "What can you do with this?"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>例如</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <color indexed="10"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr/>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <color indexed="10"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr/>
+      <t>以“这是什么？”开头，然后转到“这是什么颜色？”或“你能用它做什么？”“这是什么颜色？”或“你能用它做什么？”」</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>鉛筆やクレヨンは何が必要ですか</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <color indexed="10"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr/>
+      <t>?</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <color indexed="10"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr/>
+      <t>」</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <color indexed="10"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr/>
       <t>。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号133)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号178)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>此目标将由家庭和行为支持专家每周监测并收集数据</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>この目標は、家族や行動サポートスペシャリストによって毎週監視され、データが収集されます</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号189)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号216)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>推荐的教学策略是</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t>：</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>推奨される教育戦略は次のとおりです</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号237)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号248)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号292)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号303)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号364)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>标点符号前间距不正确</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号48)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>例如，以“这是什么？”开头，然后转到“这是什么颜色？”或“你能用它做什么？”</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>たとえば</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>「 これは何ですか</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>?</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>」 で始まります。「これは何色？」に移ります「これで何ができる？」</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>铅笔还是蜡笔，你需要什么</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>?</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>」</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号269)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>豪尔赫有时会拒绝完成某些活动，会说“不”或“因为我不想”。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>ホルヘは時々特定の活動を完了することを拒否し</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>「 いいえ」または「したくないので」と言います。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号370)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>PCA 正在帮助豪尔赫使用计时器、视觉时间表从活动中过渡，并在过渡前提供短暂的运动休息，我们将继续努力提高他的依从性。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>PCAは、ホルヘがタイマー</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>、 ビジュアルスケジュールを使用して活動から移行するのを支援し、移行前に短い移動休憩を提供しており、引き続き彼のコンプライアンスを高めていきます。</t>
+      <t>任务 1055 [英(美)译葡].docx(编号269)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>Jorge will sometimes refuse to complete certain activities and will say "No" or "because I don't want to."</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>豪尔赫有时会拒绝完成某些活动，并会说“不”或“因为我不想”。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号370)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>The PCA is helping Jorge transition from activities using timer ,visual schedule, and providing short movement breaks before transition, we will continue working to increase his compliance.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>PCA 正在帮助豪尔赫使用计时器、视觉时间表从活动中过渡，并在过渡前提供短暂的活动休息，我们将继续努力提高他的依从性。</t>
     </r>
   </si>
   <si>
@@ -2087,7 +1892,7 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号380)</t>
+      <t>任务 1055 [英(美)译葡].docx(编号380)</t>
     </r>
   </si>
   <si>
@@ -2120,13 +1925,13 @@
     </r>
     <r>
       <rPr/>
-      <t>株式会社エルウィン</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>Numeric Mismatch</t>
+      <t>ELWYN 公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>数字不匹配</t>
     </r>
   </si>
   <si>
@@ -2149,13 +1954,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号60)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>-Re-evaluation will occur every two years.</t>
+      <t>任务 1055 [英(美)译葡].docx(编号60)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>-每两年进行一次重新评估。</t>
     </r>
   </si>
   <si>
@@ -2178,13 +1983,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号64)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>use 10 different three word utterances to express his wants and needs in his classroom setting in 4 out of 5 trials</t>
+      <t>任务 1055 [英(美)译葡].docx(编号64)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>在5次尝试中，有4次在课堂上使用10种不同的三个词语来表达他的愿望和需求</t>
     </r>
   </si>
   <si>
@@ -2207,13 +2012,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号65)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>-use 5 different four word utterances to express his wants and needs in his classroom setting in 4 out of 5 trials</t>
+      <t>任务 1055 [英(美)译葡].docx(编号65)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>-在5次尝试中，有4次在课堂上使用5种不同的四个词语来表达他的愿望和需求</t>
     </r>
   </si>
   <si>
@@ -2236,13 +2041,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号66)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>-use 10 different four word utterances to express his wants and needs in his classroom setting in 4 out of 5 trials</t>
+      <t>任务 1055 [英(美)译葡].docx(编号66)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>-在5次尝试中，有4次在课堂上使用10种不同的四个词语来表达他的愿望和需求</t>
     </r>
   </si>
   <si>
@@ -2265,13 +2070,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号123)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>Progress monitoring reports will be shared with the family twice annually.</t>
+      <t>任务 1055 [英(美)译葡].docx(编号123)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>进度监测报告将每年两次与家人分享。</t>
     </r>
   </si>
   <si>
@@ -2294,19 +2099,19 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号179)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号203)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>Given verbal and visual prompts and models faded to elimination, Jorge will sustain social interaction during reciprocal play activities, with adults and peers in four out of five consecutive trials.</t>
+      <t>任务 1055 [英(美)译葡].docx(编号179)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号203)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>在口头和视觉提示以及逐渐消失的模型下，豪尔赫将在连续五次尝试中的四次中，在与成人和同伴的互动游戏活动中保持社交互动。</t>
     </r>
   </si>
   <si>
@@ -2340,13 +2145,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号228)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>-Engages in two play exchanges with an adult or child during self-selected play</t>
+      <t>任务 1055 [英(美)译葡].docx(编号228)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>-在自主选择的游戏中与成人或儿童进行两次游戏互动</t>
     </r>
   </si>
   <si>
@@ -2369,13 +2174,13 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号229)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>-Participates in a reciprocal play activity with a peer for at least three minutes</t>
+      <t>任务 1055 [英(美)译葡].docx(编号229)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>-与同伴进行至少三分钟的互动游戏活动</t>
     </r>
   </si>
   <si>
@@ -2398,93 +2203,43 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号238)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号247)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号293)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号354)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>Extra Space</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>たとえば</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>「</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>これは何ですか ? 」</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>で始まります。「これは何色？」に移ります「これで何ができる？」</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号91)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>He can imitate the play actions of adults and children; however, Jorge does not engage in reciprocal play with exchanges.</t>
+      <t>任务 1055 [英(美)译葡].docx(编号238)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号247)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号293)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号354)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>多余的空格</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号91)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>他可以模仿成人和儿童的游戏动作；然而，豪尔赫不参与互动游戏。</t>
     </r>
   </si>
   <si>
@@ -2507,86 +2262,19 @@
   <si>
     <r>
       <rPr/>
-      <t>ホルヘは時々特定の活動を完了することを拒否し</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>「</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>いいえ」または「したくないので」と言います。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>PCAは、ホルヘがタイマー</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <color indexed="10"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr/>
-      <t>ビジュアルスケジュールを使用して活動から移行するのを支援し、移行前に短い移動休憩を提供しており、引き続き彼のコンプライアンスを高めていきます。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>Repeated Words</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号32)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>What teaching strategies are needed to reach the outcome/goal?</t>
+      <t>重复的词语</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号32)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>需要哪些教学策略来实现结果/目标？</t>
     </r>
     <r>
       <rPr>
@@ -2597,7 +2285,7 @@
     </r>
     <r>
       <rPr/>
-      <t>Include specially designed instruction, supplementary aids and program personnel supports, home or program modifications and training and materials needed by the family or team.</t>
+      <t>包括专门设计的指导、辅助工具和项目人员支持、家庭或项目修改以及家庭或团队所需的培训和材料。</t>
     </r>
   </si>
   <si>
@@ -2638,31 +2326,31 @@
   <si>
     <r>
       <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号93)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号155)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号210)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号270)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>任务 1055 [英式英语译为葡萄牙语].docx(编号324)</t>
+      <t>任务 1055 [英(美)译葡].docx(编号93)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号155)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号210)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号270)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>任务 1055 [英(美)译葡].docx(编号324)</t>
     </r>
   </si>
 </sst>
